--- a/Control Signals.xlsx
+++ b/Control Signals.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Active HDL\Computer Architectuire\Pipleined_Processor_Design\Pipleined_Processor_Design\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\GitHub\ENCS4370_Pipelined_32-bit_RISC_Processor_Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FDE47F-CC63-42D4-906F-32738BAD1436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE88473-3B06-4931-8573-6C88615A61A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DBFD7B10-F6DA-4103-8936-84779C32E9AC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="61">
   <si>
     <t>OpCode</t>
   </si>
@@ -207,7 +207,7 @@
     <t>A4A3′​A2′</t>
   </si>
   <si>
-    <t>A4′A3′ + A4′A3A2′(A1 + A0′) + A4′A3A2(A1′ + A0) + A4A3′A2′A1A0</t>
+    <t>A4′​A3+A4A3′​A2′​</t>
   </si>
 </sst>
 </file>
@@ -1482,8 +1482,8 @@
       <c r="J12" s="4">
         <v>0</v>
       </c>
-      <c r="K12" s="4">
-        <v>1</v>
+      <c r="K12" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="L12" s="4">
         <v>1</v>
@@ -1553,8 +1553,8 @@
       <c r="J13" s="4">
         <v>0</v>
       </c>
-      <c r="K13" s="4">
-        <v>1</v>
+      <c r="K13" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="L13" s="4">
         <v>0</v>
@@ -1624,8 +1624,8 @@
       <c r="J14" s="4">
         <v>0</v>
       </c>
-      <c r="K14" s="4">
-        <v>1</v>
+      <c r="K14" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="L14" s="4">
         <v>0</v>
@@ -1695,8 +1695,8 @@
       <c r="J15" s="4">
         <v>0</v>
       </c>
-      <c r="K15" s="4">
-        <v>1</v>
+      <c r="K15" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="L15" s="4">
         <v>1</v>

--- a/Control Signals.xlsx
+++ b/Control Signals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\GitHub\ENCS4370_Pipelined_32-bit_RISC_Processor_Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE88473-3B06-4931-8573-6C88615A61A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91A1AF8-C5B6-4C53-A108-BB06B7A6D3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DBFD7B10-F6DA-4103-8936-84779C32E9AC}"/>
   </bookViews>
@@ -126,9 +126,6 @@
     <t>RegW</t>
   </si>
   <si>
-    <t>Z flag</t>
-  </si>
-  <si>
     <t>PCSrc</t>
   </si>
   <si>
@@ -150,18 +147,9 @@
     <t>Suppose Opcode = A</t>
   </si>
   <si>
-    <t>A4′​A3′​A1′​A0+A1′​A2A3</t>
-  </si>
-  <si>
     <t>A4​+A2​A1​+(A1​⊕A0​)</t>
   </si>
   <si>
-    <t>A4​+A3′​A2′​A1​A0′​+A3′​A2​A1′​+A0​(A3​⊕A2​)</t>
-  </si>
-  <si>
-    <t>A4′​A3′​+A4′​A1′​A0′​+(A2​⊕A1​)+A1​A0​</t>
-  </si>
-  <si>
     <t>A3</t>
   </si>
   <si>
@@ -177,27 +165,12 @@
     <t>Wbdata0</t>
   </si>
   <si>
-    <t>A4+A3A2′A1′</t>
-  </si>
-  <si>
     <t>PCSrc0</t>
   </si>
   <si>
     <t>PCSrc1</t>
   </si>
   <si>
-    <t>A3​(A2​⊕A1​)′​+A1′​A0​</t>
-  </si>
-  <si>
-    <t>A3A2′​A1′​A0+A4A1</t>
-  </si>
-  <si>
-    <t>PCSrc1​=A3​A2′​A1′​A0​+A4​A1′​(Z⊕A0​)</t>
-  </si>
-  <si>
-    <t>A4​+A3′​A2​A0′​+(A3′​​+A2​)​(A1​⊕A0​)′​</t>
-  </si>
-  <si>
     <t>RegSrc</t>
   </si>
   <si>
@@ -207,7 +180,34 @@
     <t>A4A3′​A2′</t>
   </si>
   <si>
-    <t>A4′​A3+A4A3′​A2′​</t>
+    <t>A4′A3′ + A4′A3A2′(A1 + A0′) + A4′A3A2(A1′ + A0) + A4A3′A2′A1A0</t>
+  </si>
+  <si>
+    <t>A4′A3 + A4A3′A2′</t>
+  </si>
+  <si>
+    <t>A4′A3A2′A1′ + A4A3′A2′</t>
+  </si>
+  <si>
+    <t>A4′A3A2′A1′ + A4′A3A2A0</t>
+  </si>
+  <si>
+    <t>A4′A3′A2A1 + A4′A3′A1′A0</t>
+  </si>
+  <si>
+    <t>A4′A3′A2A0′ + A4′A3′A1A0 + A4′A2A1′A0′ + A4A3′A2′</t>
+  </si>
+  <si>
+    <t>A4′A3′A2A1′ + A4′A3′A2A0 + A4′A3A2′A0 + A4A3′A2′ + A3′A2′A1A0′</t>
+  </si>
+  <si>
+    <t>A3A2′A1′A0 + A4A1′(Equal ⊕ A0)</t>
+  </si>
+  <si>
+    <t>A3A2′A1′A0 + A4A1</t>
+  </si>
+  <si>
+    <t>EQ</t>
   </si>
 </sst>
 </file>
@@ -667,7 +667,7 @@
     <col min="22" max="22" width="10.59765625" customWidth="1"/>
     <col min="24" max="24" width="21.5" customWidth="1"/>
     <col min="25" max="25" width="21.19921875" customWidth="1"/>
-    <col min="26" max="26" width="68.59765625" customWidth="1"/>
+    <col min="26" max="26" width="79.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -699,13 +699,13 @@
         <v>25</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>26</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N1" s="6" t="s">
         <v>27</v>
@@ -729,19 +729,19 @@
         <v>3</v>
       </c>
       <c r="V1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="W1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z3" s="4" t="s">
         <v>56</v>
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1025,7 +1025,7 @@
         <v>25</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1167,7 +1167,7 @@
         <v>26</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1238,7 +1238,7 @@
         <v>32</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1309,7 +1309,7 @@
         <v>27</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1380,7 +1380,7 @@
         <v>30</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1451,7 +1451,7 @@
         <v>28</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1519,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1590,10 +1590,10 @@
         <v>0</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1661,10 +1661,10 @@
         <v>0</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="18" x14ac:dyDescent="0.25">
@@ -1732,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="18" x14ac:dyDescent="0.25">
